--- a/data/trans_camb/IP1001-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP1001-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,78; 2,19</t>
+          <t>-4,0; 2,1</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,48; 0,43</t>
+          <t>-5,53; 0,26</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,58; -0,42</t>
+          <t>-5,86; -0,42</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,58; 0,63</t>
+          <t>-4,58; 0,84</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-5,36; 0,69</t>
+          <t>-4,68; 0,65</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-4,06; 2,88</t>
+          <t>-4,14; 2,42</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 0,86</t>
+          <t>-3,27; 0,81</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,88; -0,04</t>
+          <t>-3,76; -0,0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 0,24</t>
+          <t>-3,57; 0,31</t>
         </is>
       </c>
     </row>
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-83,98; 99,39</t>
+          <t>-87,31; 115,67</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-94,44; 44,65</t>
+          <t>-100,0; 36,28</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 720,51</t>
+          <t>-100,0; 106,58</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 2,67</t>
+          <t>-0,85; 2,79</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 3,19</t>
+          <t>-0,66; 3,01</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 3,23</t>
+          <t>-0,67; 3,68</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 3,49</t>
+          <t>-0,43; 3,54</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 2,71</t>
+          <t>-0,92; 2,69</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 3,3</t>
+          <t>-1,08; 3,25</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 2,57</t>
+          <t>-0,17; 2,5</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 2,3</t>
+          <t>-0,31; 2,3</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 2,67</t>
+          <t>-0,53; 2,35</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-73,66; 839,87</t>
+          <t>-65,12; 730,51</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-54,43; 1124,59</t>
+          <t>-64,52; 768,25</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-71,65; 881,58</t>
+          <t>-74,9; 964,54</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-37,7; 704,58</t>
+          <t>-37,8; 613,56</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-62,62; 417,9</t>
+          <t>-50,27; 478,71</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-71,22; 744,59</t>
+          <t>-69,54; 642,79</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-19,14; 381,85</t>
+          <t>-17,96; 388,88</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-26,67; 338,63</t>
+          <t>-26,48; 360,53</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-38,09; 400,63</t>
+          <t>-38,84; 368,4</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,67; -0,03</t>
+          <t>-6,15; 0,19</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,61; 3,88</t>
+          <t>-3,69; 4,05</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,51; 1,81</t>
+          <t>-5,08; 1,83</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,43; 1,62</t>
+          <t>-5,35; 1,25</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,32; 2,4</t>
+          <t>-4,88; 2,2</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 6,28</t>
+          <t>-3,49; 5,16</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,98; -0,16</t>
+          <t>-4,76; -0,17</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 2,26</t>
+          <t>-2,79; 2,26</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 2,86</t>
+          <t>-3,38; 2,99</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-93,61; 27,83</t>
+          <t>-100,0; 39,17</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-59,04; 172,56</t>
+          <t>-60,25; 182,89</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-83,38; 89,0</t>
+          <t>-78,41; 120,06</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-85,87; 84,14</t>
+          <t>-85,58; 73,43</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-70,33; 116,99</t>
+          <t>-73,91; 93,83</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-64,41; 281,39</t>
+          <t>-64,36; 208,47</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-81,72; 9,6</t>
+          <t>-82,05; -0,26</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-50,72; 77,26</t>
+          <t>-50,01; 81,02</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-62,6; 103,85</t>
+          <t>-61,64; 101,16</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,2; 0,5</t>
+          <t>-6,1; 0,57</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-7,18; -1,52</t>
+          <t>-7,38; -1,49</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,31; -0,32</t>
+          <t>-6,24; -0,01</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 4,28</t>
+          <t>-2,2; 4,31</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 3,6</t>
+          <t>-2,58; 3,35</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 3,98</t>
+          <t>-1,93; 3,64</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 1,49</t>
+          <t>-3,06; 1,35</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,92; 0,3</t>
+          <t>-3,94; 0,07</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 1,09</t>
+          <t>-3,01; 1,24</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-84,39; 24,26</t>
+          <t>-83,53; 47,06</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-95,09; -27,45</t>
+          <t>-96,07; -18,38</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-83,53; 0,35</t>
+          <t>-84,59; 5,44</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-45,49; 213,15</t>
+          <t>-51,37; 224,41</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-68,14; 205,97</t>
+          <t>-61,13; 178,87</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-44,19; 242,13</t>
+          <t>-46,62; 185,07</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-59,19; 42,74</t>
+          <t>-56,35; 45,55</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-74,01; 13,25</t>
+          <t>-74,76; 7,49</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-57,51; 37,56</t>
+          <t>-54,28; 40,9</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 0,22</t>
+          <t>-2,44; 0,23</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 0,61</t>
+          <t>-2,23; 0,7</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 0,65</t>
+          <t>-2,14; 0,59</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 1,36</t>
+          <t>-1,23; 1,38</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 1,29</t>
+          <t>-1,51; 1,2</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 2,85</t>
+          <t>-0,7; 2,68</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 0,53</t>
+          <t>-1,5; 0,42</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 0,59</t>
+          <t>-1,44; 0,48</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 1,32</t>
+          <t>-1,02; 1,23</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-66,07; 12,02</t>
+          <t>-63,4; 12,87</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-58,05; 29,17</t>
+          <t>-58,09; 36,04</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-62,58; 33,31</t>
+          <t>-59,0; 30,14</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-40,66; 67,42</t>
+          <t>-37,85; 68,7</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-44,02; 64,61</t>
+          <t>-43,53; 59,2</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-20,14; 135,14</t>
+          <t>-25,29; 127,23</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-44,99; 20,53</t>
+          <t>-43,62; 18,5</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-43,15; 26,0</t>
+          <t>-42,82; 19,93</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-29,12; 56,22</t>
+          <t>-32,11; 49,66</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1001-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP1001-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,0; 2,1</t>
+          <t>-3,88; 2,11</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,53; 0,26</t>
+          <t>-5,01; 0,05</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,86; -0,42</t>
+          <t>-5,78; -0,66</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,58; 0,84</t>
+          <t>-5,09; 0,66</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,68; 0,65</t>
+          <t>-5,53; 0,6</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-4,14; 2,42</t>
+          <t>-4,39; 2,3</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,27; 0,81</t>
+          <t>-3,21; 0,86</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,76; -0,0</t>
+          <t>-3,59; 0,09</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-3,57; 0,31</t>
+          <t>-3,67; 0,34</t>
         </is>
       </c>
     </row>
@@ -803,27 +803,27 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
+          <t>-100,0; 167,52</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-87,31; 115,67</t>
+          <t>-83,19; 131,03</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 36,28</t>
+          <t>-100,0; 49,69</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 106,58</t>
+          <t>-100,0; 293,8</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 2,79</t>
+          <t>-0,79; 3,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 3,01</t>
+          <t>-0,65; 3,07</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 3,68</t>
+          <t>-0,71; 3,35</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 3,54</t>
+          <t>-0,37; 3,58</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 2,69</t>
+          <t>-0,84; 2,74</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 3,25</t>
+          <t>-1,21; 3,09</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 2,5</t>
+          <t>-0,24; 2,52</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 2,3</t>
+          <t>-0,26; 2,26</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 2,35</t>
+          <t>-0,52; 2,53</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-65,12; 730,51</t>
+          <t>-73,92; 920,72</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-64,52; 768,25</t>
+          <t>-57,3; 903,79</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-74,9; 964,54</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-37,8; 613,56</t>
+          <t>-33,1; 592,65</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-50,27; 478,71</t>
+          <t>-54,35; 528,43</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-69,54; 642,79</t>
+          <t>-79,8; 563,14</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-17,96; 388,88</t>
+          <t>-24,26; 371,55</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-26,48; 360,53</t>
+          <t>-20,12; 353,31</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-38,84; 368,4</t>
+          <t>-41,26; 335,28</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,15; 0,19</t>
+          <t>-6,36; -0,02</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,69; 4,05</t>
+          <t>-3,58; 4,09</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,08; 1,83</t>
+          <t>-5,13; 1,99</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,35; 1,25</t>
+          <t>-5,19; 1,72</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,88; 2,2</t>
+          <t>-4,37; 2,58</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 5,16</t>
+          <t>-3,62; 6,52</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,76; -0,17</t>
+          <t>-4,99; -0,03</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 2,26</t>
+          <t>-2,79; 2,41</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 2,99</t>
+          <t>-3,33; 2,78</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 39,17</t>
+          <t>-100,0; 44,9</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-60,25; 182,89</t>
+          <t>-58,16; 166,94</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-78,41; 120,06</t>
+          <t>-82,66; 109,75</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-85,58; 73,43</t>
+          <t>-85,75; 93,54</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-73,91; 93,83</t>
+          <t>-69,18; 129,56</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-64,36; 208,47</t>
+          <t>-65,96; 277,44</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-82,05; -0,26</t>
+          <t>-83,06; 12,44</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-50,01; 81,02</t>
+          <t>-48,68; 93,43</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-61,64; 101,16</t>
+          <t>-59,87; 95,99</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,1; 0,57</t>
+          <t>-6,24; 0,07</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-7,38; -1,49</t>
+          <t>-7,18; -1,5</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,24; -0,01</t>
+          <t>-6,15; -0,01</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 4,31</t>
+          <t>-1,95; 4,24</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 3,35</t>
+          <t>-2,87; 3,55</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 3,64</t>
+          <t>-2,0; 4,39</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 1,35</t>
+          <t>-3,22; 1,54</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,94; 0,07</t>
+          <t>-4,01; 0,15</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 1,24</t>
+          <t>-2,98; 1,25</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-83,53; 47,06</t>
+          <t>-85,81; 11,94</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-96,07; -18,38</t>
+          <t>-95,46; -29,17</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-84,59; 5,44</t>
+          <t>-83,12; 11,74</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-51,37; 224,41</t>
+          <t>-48,48; 214,53</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-61,13; 178,87</t>
+          <t>-61,77; 175,83</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-46,62; 185,07</t>
+          <t>-44,91; 225,89</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-56,35; 45,55</t>
+          <t>-60,13; 52,7</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-74,76; 7,49</t>
+          <t>-74,7; 8,43</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-54,28; 40,9</t>
+          <t>-54,37; 40,78</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 0,23</t>
+          <t>-2,57; 0,19</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 0,7</t>
+          <t>-2,17; 0,51</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 0,59</t>
+          <t>-2,24; 0,45</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 1,38</t>
+          <t>-1,28; 1,37</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 1,2</t>
+          <t>-1,4; 1,27</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 2,68</t>
+          <t>-0,54; 2,94</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 0,42</t>
+          <t>-1,51; 0,45</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 0,48</t>
+          <t>-1,33; 0,56</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 1,23</t>
+          <t>-0,97; 1,28</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-63,4; 12,87</t>
+          <t>-67,68; 12,23</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-58,09; 36,04</t>
+          <t>-56,88; 24,42</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-59,0; 30,14</t>
+          <t>-60,09; 20,88</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-37,85; 68,7</t>
+          <t>-39,36; 68,5</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-43,53; 59,2</t>
+          <t>-43,08; 65,68</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-25,29; 127,23</t>
+          <t>-18,25; 140,99</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-43,62; 18,5</t>
+          <t>-44,83; 20,45</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-42,82; 19,93</t>
+          <t>-39,6; 24,37</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-32,11; 49,66</t>
+          <t>-29,83; 55,89</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1001-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP1001-Edad-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,34 +624,34 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-1,52</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-1,47</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-1,15</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>-0,25</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-1,56</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>-2,02</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-1,52</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-1,47</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-1,24</t>
-        </is>
-      </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
           <t>-0,9</t>
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-1,63</t>
+          <t>-1,61</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,88; 2,11</t>
+          <t>-4,58; 0,63</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,01; 0,05</t>
+          <t>-5,36; 0,69</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,78; -0,66</t>
+          <t>-3,78; 3,63</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,09; 0,66</t>
+          <t>-3,78; 2,19</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-5,53; 0,6</t>
+          <t>-5,48; 0,43</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-4,39; 2,3</t>
+          <t>-6,58; -0,42</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 0,86</t>
+          <t>-3,19; 0,86</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,59; 0,09</t>
+          <t>-3,88; -0,04</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 0,34</t>
+          <t>-3,8; 0,29</t>
         </is>
       </c>
     </row>
@@ -730,34 +730,34 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-62,92%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-60,66%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-47,43%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>-12,51%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-77,3%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-62,92%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-60,66%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-51,38%</t>
-        </is>
-      </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
           <t>-40,24%</t>
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-72,78%</t>
+          <t>-71,94%</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 167,52</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-83,19; 131,03</t>
+          <t>-83,98; 99,39</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 49,69</t>
+          <t>-94,44; 44,65</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 293,8</t>
+          <t>-100,0; inf</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1,42</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,89</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0,8</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>0,79</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>1,02</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,94</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1,42</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,89</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,69</t>
+          <t>1,12</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,82</t>
+          <t>0,96</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 3,0</t>
+          <t>-0,4; 3,49</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 3,07</t>
+          <t>-1,1; 2,71</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 3,35</t>
+          <t>-1,04; 3,63</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 3,58</t>
+          <t>-0,88; 2,67</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 2,74</t>
+          <t>-0,63; 3,19</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 3,09</t>
+          <t>-0,67; 3,67</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 2,52</t>
+          <t>-0,14; 2,57</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 2,26</t>
+          <t>-0,37; 2,3</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 2,53</t>
+          <t>-0,47; 2,95</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>108,19%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>67,68%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>61,2%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>76,84%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>92,24%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>108,19%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>67,68%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>52,84%</t>
+          <t>109,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>70,2%</t>
+          <t>82,32%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-73,92; 920,72</t>
+          <t>-37,7; 704,58</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-57,3; 903,79</t>
+          <t>-62,62; 417,9</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-73,99; 769,18</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-33,1; 592,65</t>
+          <t>-73,66; 839,87</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-54,35; 528,43</t>
+          <t>-54,43; 1124,59</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-79,8; 563,14</t>
+          <t>-70,61; 980,54</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-24,26; 371,55</t>
+          <t>-19,14; 381,85</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-20,12; 353,31</t>
+          <t>-26,67; 338,63</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-41,26; 335,28</t>
+          <t>-33,81; 442,34</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-1,88</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-0,97</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-0,98</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>-2,88</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>0,3</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-1,6</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-1,88</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-0,97</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,1</t>
+          <t>-1,49</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-0,66</t>
+          <t>-1,22</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,36; -0,02</t>
+          <t>-5,43; 1,62</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,58; 4,09</t>
+          <t>-4,32; 2,4</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,13; 1,99</t>
+          <t>-4,43; 2,78</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,19; 1,72</t>
+          <t>-6,67; -0,03</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,37; 2,58</t>
+          <t>-3,61; 3,88</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,62; 6,52</t>
+          <t>-5,6; 1,86</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,99; -0,03</t>
+          <t>-4,98; -0,16</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 2,41</t>
+          <t>-3,02; 2,26</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-3,33; 2,78</t>
+          <t>-3,93; 1,24</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-43,31%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-22,44%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-22,7%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>-66,27%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>6,96%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-36,76%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-43,31%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-22,44%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>-34,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-15,27%</t>
+          <t>-28,16%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 44,9</t>
+          <t>-85,87; 84,14</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-58,16; 166,94</t>
+          <t>-70,33; 116,99</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-82,66; 109,75</t>
+          <t>-70,23; 150,35</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-85,75; 93,54</t>
+          <t>-93,61; 27,83</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-69,18; 129,56</t>
+          <t>-59,04; 172,56</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-65,96; 277,44</t>
+          <t>-83,24; 97,95</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-83,06; 12,44</t>
+          <t>-81,72; 9,6</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-48,68; 93,43</t>
+          <t>-50,72; 77,26</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-59,87; 95,99</t>
+          <t>-66,62; 43,79</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0,89</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0,15</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1,07</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>-2,74</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-4,09</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-3,03</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0,89</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>0,15</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,03</t>
+          <t>-2,75</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-0,92</t>
+          <t>-0,75</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,24; 0,07</t>
+          <t>-2,0; 4,28</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-7,18; -1,5</t>
+          <t>-3,09; 3,6</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,15; -0,01</t>
+          <t>-2,05; 4,05</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 4,24</t>
+          <t>-6,2; 0,5</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,87; 3,55</t>
+          <t>-7,18; -1,52</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 4,39</t>
+          <t>-6,03; 0,18</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 1,54</t>
+          <t>-3,04; 1,49</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 0,15</t>
+          <t>-3,92; 0,3</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-2,98; 1,25</t>
+          <t>-2,88; 1,21</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>26,6%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>4,4%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>31,97%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>-51,9%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-77,26%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-57,34%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>26,6%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>4,4%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>30,96%</t>
+          <t>-52,08%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-21,35%</t>
+          <t>-17,55%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-85,81; 11,94</t>
+          <t>-45,49; 213,15</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-95,46; -29,17</t>
+          <t>-68,14; 205,97</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-83,12; 11,74</t>
+          <t>-44,88; 245,13</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-48,48; 214,53</t>
+          <t>-84,39; 24,26</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-61,77; 175,83</t>
+          <t>-95,09; -27,45</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-44,91; 225,89</t>
+          <t>-80,44; 17,61</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-60,13; 52,7</t>
+          <t>-59,19; 42,74</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-74,7; 8,43</t>
+          <t>-74,01; 13,25</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-54,37; 40,78</t>
+          <t>-53,63; 44,95</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>0,01</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-0,08</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0,7</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>-1,11</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>-0,78</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-0,9</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>0,01</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-0,08</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,9</t>
+          <t>-0,69</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0,05</t>
+          <t>0,03</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 0,19</t>
+          <t>-1,37; 1,36</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 0,51</t>
+          <t>-1,42; 1,29</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 0,45</t>
+          <t>-0,81; 2,26</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 1,37</t>
+          <t>-2,49; 0,22</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 1,27</t>
+          <t>-2,14; 0,61</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 2,94</t>
+          <t>-2,23; 0,91</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 0,45</t>
+          <t>-1,51; 0,53</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 0,56</t>
+          <t>-1,46; 0,59</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 1,28</t>
+          <t>-1,01; 1,17</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>0,21%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-3,09%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>26,11%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>-36,91%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>-25,79%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-29,74%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>0,21%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-3,09%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>-23,04%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,21%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-67,68; 12,23</t>
+          <t>-40,66; 67,42</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-56,88; 24,42</t>
+          <t>-44,02; 64,61</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-60,09; 20,88</t>
+          <t>-25,31; 110,47</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-39,36; 68,5</t>
+          <t>-66,07; 12,02</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-43,08; 65,68</t>
+          <t>-58,05; 29,17</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-18,25; 140,99</t>
+          <t>-58,9; 43,52</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-44,83; 20,45</t>
+          <t>-44,99; 20,53</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-39,6; 24,37</t>
+          <t>-43,15; 26,0</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-29,83; 55,89</t>
+          <t>-32,25; 52,22</t>
         </is>
       </c>
     </row>
